--- a/backend/Students.xlsx
+++ b/backend/Students.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>Final Exam</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Assessments Completed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -500,6 +505,9 @@
       <c r="I2" t="n">
         <v>93.5</v>
       </c>
+      <c r="J2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -531,6 +539,9 @@
       <c r="I3" t="n">
         <v>51.9</v>
       </c>
+      <c r="J3" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -562,6 +573,9 @@
       <c r="I4" t="n">
         <v>88.3</v>
       </c>
+      <c r="J4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -593,6 +607,9 @@
       <c r="I5" t="n">
         <v>45.8</v>
       </c>
+      <c r="J5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -624,6 +641,9 @@
       <c r="I6" t="n">
         <v>62.7</v>
       </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -655,6 +675,9 @@
       <c r="I7" t="n">
         <v>42.7</v>
       </c>
+      <c r="J7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -686,6 +709,9 @@
       <c r="I8" t="n">
         <v>78.09999999999999</v>
       </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -717,6 +743,9 @@
       <c r="I9" t="n">
         <v>76.5</v>
       </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -748,6 +777,9 @@
       <c r="I10" t="n">
         <v>73.40000000000001</v>
       </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -779,6 +811,9 @@
       <c r="I11" t="n">
         <v>56.1</v>
       </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -810,6 +845,9 @@
       <c r="I12" t="n">
         <v>94.90000000000001</v>
       </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -841,6 +879,9 @@
       <c r="I13" t="n">
         <v>93.90000000000001</v>
       </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -872,6 +913,9 @@
       <c r="I14" t="n">
         <v>46.6</v>
       </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -903,6 +947,9 @@
       <c r="I15" t="n">
         <v>71.7</v>
       </c>
+      <c r="J15" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -934,6 +981,9 @@
       <c r="I16" t="n">
         <v>56</v>
       </c>
+      <c r="J16" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -965,6 +1015,9 @@
       <c r="I17" t="n">
         <v>55.8</v>
       </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -996,6 +1049,9 @@
       <c r="I18" t="n">
         <v>76.5</v>
       </c>
+      <c r="J18" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1027,6 +1083,9 @@
       <c r="I19" t="n">
         <v>59.4</v>
       </c>
+      <c r="J19" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1058,6 +1117,9 @@
       <c r="I20" t="n">
         <v>92.7</v>
       </c>
+      <c r="J20" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1089,6 +1151,9 @@
       <c r="I21" t="n">
         <v>47.7</v>
       </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1120,6 +1185,9 @@
       <c r="I22" t="n">
         <v>72.40000000000001</v>
       </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1151,6 +1219,9 @@
       <c r="I23" t="n">
         <v>71.09999999999999</v>
       </c>
+      <c r="J23" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1182,6 +1253,9 @@
       <c r="I24" t="n">
         <v>44.3</v>
       </c>
+      <c r="J24" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1213,6 +1287,9 @@
       <c r="I25" t="n">
         <v>80.09999999999999</v>
       </c>
+      <c r="J25" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1244,6 +1321,9 @@
       <c r="I26" t="n">
         <v>88.40000000000001</v>
       </c>
+      <c r="J26" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1275,6 +1355,9 @@
       <c r="I27" t="n">
         <v>80.40000000000001</v>
       </c>
+      <c r="J27" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1306,6 +1389,9 @@
       <c r="I28" t="n">
         <v>51.4</v>
       </c>
+      <c r="J28" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1337,6 +1423,9 @@
       <c r="I29" t="n">
         <v>91.7</v>
       </c>
+      <c r="J29" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1368,6 +1457,9 @@
       <c r="I30" t="n">
         <v>90.90000000000001</v>
       </c>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1399,6 +1491,9 @@
       <c r="I31" t="n">
         <v>99.09999999999999</v>
       </c>
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1430,6 +1525,9 @@
       <c r="I32" t="n">
         <v>73.3</v>
       </c>
+      <c r="J32" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1461,6 +1559,9 @@
       <c r="I33" t="n">
         <v>84.90000000000001</v>
       </c>
+      <c r="J33" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1492,6 +1593,9 @@
       <c r="I34" t="n">
         <v>44.8</v>
       </c>
+      <c r="J34" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1523,6 +1627,9 @@
       <c r="I35" t="n">
         <v>54.8</v>
       </c>
+      <c r="J35" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1554,6 +1661,9 @@
       <c r="I36" t="n">
         <v>52.3</v>
       </c>
+      <c r="J36" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1585,6 +1695,9 @@
       <c r="I37" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="J37" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1616,6 +1729,9 @@
       <c r="I38" t="n">
         <v>55.9</v>
       </c>
+      <c r="J38" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1647,6 +1763,9 @@
       <c r="I39" t="n">
         <v>82.2</v>
       </c>
+      <c r="J39" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1678,6 +1797,9 @@
       <c r="I40" t="n">
         <v>79.8</v>
       </c>
+      <c r="J40" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1709,6 +1831,9 @@
       <c r="I41" t="n">
         <v>76.3</v>
       </c>
+      <c r="J41" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1740,6 +1865,9 @@
       <c r="I42" t="n">
         <v>90.8</v>
       </c>
+      <c r="J42" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1771,6 +1899,9 @@
       <c r="I43" t="n">
         <v>55.7</v>
       </c>
+      <c r="J43" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1802,6 +1933,9 @@
       <c r="I44" t="n">
         <v>94.2</v>
       </c>
+      <c r="J44" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1833,6 +1967,9 @@
       <c r="I45" t="n">
         <v>93.90000000000001</v>
       </c>
+      <c r="J45" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1864,6 +2001,9 @@
       <c r="I46" t="n">
         <v>86.8</v>
       </c>
+      <c r="J46" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1895,6 +2035,9 @@
       <c r="I47" t="n">
         <v>98.59999999999999</v>
       </c>
+      <c r="J47" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1926,6 +2069,9 @@
       <c r="I48" t="n">
         <v>88.09999999999999</v>
       </c>
+      <c r="J48" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1957,6 +2103,9 @@
       <c r="I49" t="n">
         <v>91.5</v>
       </c>
+      <c r="J49" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1988,6 +2137,9 @@
       <c r="I50" t="n">
         <v>41.4</v>
       </c>
+      <c r="J50" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2019,6 +2171,9 @@
       <c r="I51" t="n">
         <v>64</v>
       </c>
+      <c r="J51" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2050,6 +2205,9 @@
       <c r="I52" t="n">
         <v>97.8</v>
       </c>
+      <c r="J52" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2081,6 +2239,9 @@
       <c r="I53" t="n">
         <v>70.7</v>
       </c>
+      <c r="J53" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2112,6 +2273,9 @@
       <c r="I54" t="n">
         <v>72.3</v>
       </c>
+      <c r="J54" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2143,6 +2307,9 @@
       <c r="I55" t="n">
         <v>59.8</v>
       </c>
+      <c r="J55" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2174,6 +2341,9 @@
       <c r="I56" t="n">
         <v>64.09999999999999</v>
       </c>
+      <c r="J56" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2205,6 +2375,9 @@
       <c r="I57" t="n">
         <v>76.90000000000001</v>
       </c>
+      <c r="J57" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2236,6 +2409,9 @@
       <c r="I58" t="n">
         <v>79.3</v>
       </c>
+      <c r="J58" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2267,6 +2443,9 @@
       <c r="I59" t="n">
         <v>50.2</v>
       </c>
+      <c r="J59" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2298,6 +2477,9 @@
       <c r="I60" t="n">
         <v>80.40000000000001</v>
       </c>
+      <c r="J60" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2329,6 +2511,9 @@
       <c r="I61" t="n">
         <v>44.4</v>
       </c>
+      <c r="J61" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2360,6 +2545,9 @@
       <c r="I62" t="n">
         <v>79.40000000000001</v>
       </c>
+      <c r="J62" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2391,6 +2579,9 @@
       <c r="I63" t="n">
         <v>97.5</v>
       </c>
+      <c r="J63" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2422,6 +2613,9 @@
       <c r="I64" t="n">
         <v>80.09999999999999</v>
       </c>
+      <c r="J64" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2453,6 +2647,9 @@
       <c r="I65" t="n">
         <v>70.3</v>
       </c>
+      <c r="J65" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2484,6 +2681,9 @@
       <c r="I66" t="n">
         <v>54.8</v>
       </c>
+      <c r="J66" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2515,6 +2715,9 @@
       <c r="I67" t="n">
         <v>57.1</v>
       </c>
+      <c r="J67" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2546,6 +2749,9 @@
       <c r="I68" t="n">
         <v>82.40000000000001</v>
       </c>
+      <c r="J68" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2577,6 +2783,9 @@
       <c r="I69" t="n">
         <v>94.3</v>
       </c>
+      <c r="J69" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2608,6 +2817,9 @@
       <c r="I70" t="n">
         <v>61.1</v>
       </c>
+      <c r="J70" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2639,6 +2851,9 @@
       <c r="I71" t="n">
         <v>76.2</v>
       </c>
+      <c r="J71" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2670,6 +2885,9 @@
       <c r="I72" t="n">
         <v>64.3</v>
       </c>
+      <c r="J72" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2701,6 +2919,9 @@
       <c r="I73" t="n">
         <v>73.90000000000001</v>
       </c>
+      <c r="J73" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2732,6 +2953,9 @@
       <c r="I74" t="n">
         <v>52.7</v>
       </c>
+      <c r="J74" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2763,6 +2987,9 @@
       <c r="I75" t="n">
         <v>44.9</v>
       </c>
+      <c r="J75" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2794,6 +3021,9 @@
       <c r="I76" t="n">
         <v>79.09999999999999</v>
       </c>
+      <c r="J76" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2825,6 +3055,9 @@
       <c r="I77" t="n">
         <v>80.2</v>
       </c>
+      <c r="J77" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2856,6 +3089,9 @@
       <c r="I78" t="n">
         <v>84.90000000000001</v>
       </c>
+      <c r="J78" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2887,6 +3123,9 @@
       <c r="I79" t="n">
         <v>80.59999999999999</v>
       </c>
+      <c r="J79" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2918,6 +3157,9 @@
       <c r="I80" t="n">
         <v>46.1</v>
       </c>
+      <c r="J80" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2949,6 +3191,9 @@
       <c r="I81" t="n">
         <v>60.8</v>
       </c>
+      <c r="J81" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2980,6 +3225,9 @@
       <c r="I82" t="n">
         <v>46.3</v>
       </c>
+      <c r="J82" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3011,6 +3259,9 @@
       <c r="I83" t="n">
         <v>97.90000000000001</v>
       </c>
+      <c r="J83" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3042,6 +3293,9 @@
       <c r="I84" t="n">
         <v>56.1</v>
       </c>
+      <c r="J84" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3073,6 +3327,9 @@
       <c r="I85" t="n">
         <v>76.59999999999999</v>
       </c>
+      <c r="J85" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3104,6 +3361,9 @@
       <c r="I86" t="n">
         <v>60.4</v>
       </c>
+      <c r="J86" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3135,6 +3395,9 @@
       <c r="I87" t="n">
         <v>83.2</v>
       </c>
+      <c r="J87" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3166,6 +3429,9 @@
       <c r="I88" t="n">
         <v>45.6</v>
       </c>
+      <c r="J88" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3197,6 +3463,9 @@
       <c r="I89" t="n">
         <v>65.5</v>
       </c>
+      <c r="J89" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3228,6 +3497,9 @@
       <c r="I90" t="n">
         <v>51.6</v>
       </c>
+      <c r="J90" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3258,6 +3530,9 @@
       </c>
       <c r="I91" t="n">
         <v>83.5</v>
+      </c>
+      <c r="J91" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3271,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3325,6 +3600,11 @@
           <t>Final Exam</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Assessments Completed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -3359,6 +3639,9 @@
       <c r="J2" t="n">
         <v>40.8</v>
       </c>
+      <c r="K2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3393,6 +3676,9 @@
       <c r="J3" t="n">
         <v>69.5</v>
       </c>
+      <c r="K3" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3427,6 +3713,9 @@
       <c r="J4" t="n">
         <v>68.7</v>
       </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3461,6 +3750,9 @@
       <c r="J5" t="n">
         <v>58.2</v>
       </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3495,6 +3787,9 @@
       <c r="J6" t="n">
         <v>67</v>
       </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3529,6 +3824,9 @@
       <c r="J7" t="n">
         <v>96.90000000000001</v>
       </c>
+      <c r="K7" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3563,6 +3861,9 @@
       <c r="J8" t="n">
         <v>67</v>
       </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3597,6 +3898,9 @@
       <c r="J9" t="n">
         <v>95.40000000000001</v>
       </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3631,6 +3935,9 @@
       <c r="J10" t="n">
         <v>94.5</v>
       </c>
+      <c r="K10" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3665,6 +3972,9 @@
       <c r="J11" t="n">
         <v>47.5</v>
       </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3699,6 +4009,9 @@
       <c r="J12" t="n">
         <v>65.90000000000001</v>
       </c>
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3733,6 +4046,9 @@
       <c r="J13" t="n">
         <v>100</v>
       </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3767,6 +4083,9 @@
       <c r="J14" t="n">
         <v>50.9</v>
       </c>
+      <c r="K14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3801,6 +4120,9 @@
       <c r="J15" t="n">
         <v>91.5</v>
       </c>
+      <c r="K15" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3835,6 +4157,9 @@
       <c r="J16" t="n">
         <v>58.9</v>
       </c>
+      <c r="K16" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3869,6 +4194,9 @@
       <c r="J17" t="n">
         <v>64.8</v>
       </c>
+      <c r="K17" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3903,6 +4231,9 @@
       <c r="J18" t="n">
         <v>95.7</v>
       </c>
+      <c r="K18" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3937,6 +4268,9 @@
       <c r="J19" t="n">
         <v>73.09999999999999</v>
       </c>
+      <c r="K19" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3971,6 +4305,9 @@
       <c r="J20" t="n">
         <v>69.90000000000001</v>
       </c>
+      <c r="K20" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4005,6 +4342,9 @@
       <c r="J21" t="n">
         <v>63</v>
       </c>
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4039,6 +4379,9 @@
       <c r="J22" t="n">
         <v>96.09999999999999</v>
       </c>
+      <c r="K22" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4073,6 +4416,9 @@
       <c r="J23" t="n">
         <v>48.9</v>
       </c>
+      <c r="K23" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4107,6 +4453,9 @@
       <c r="J24" t="n">
         <v>81.8</v>
       </c>
+      <c r="K24" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4141,6 +4490,9 @@
       <c r="J25" t="n">
         <v>63.2</v>
       </c>
+      <c r="K25" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4175,6 +4527,9 @@
       <c r="J26" t="n">
         <v>92.2</v>
       </c>
+      <c r="K26" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4209,6 +4564,9 @@
       <c r="J27" t="n">
         <v>49.3</v>
       </c>
+      <c r="K27" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4243,6 +4601,9 @@
       <c r="J28" t="n">
         <v>91.59999999999999</v>
       </c>
+      <c r="K28" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4277,6 +4638,9 @@
       <c r="J29" t="n">
         <v>77.90000000000001</v>
       </c>
+      <c r="K29" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4311,6 +4675,9 @@
       <c r="J30" t="n">
         <v>66.59999999999999</v>
       </c>
+      <c r="K30" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4345,6 +4712,9 @@
       <c r="J31" t="n">
         <v>71.90000000000001</v>
       </c>
+      <c r="K31" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4379,6 +4749,9 @@
       <c r="J32" t="n">
         <v>94.8</v>
       </c>
+      <c r="K32" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4413,6 +4786,9 @@
       <c r="J33" t="n">
         <v>80.7</v>
       </c>
+      <c r="K33" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4447,6 +4823,9 @@
       <c r="J34" t="n">
         <v>90.7</v>
       </c>
+      <c r="K34" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4481,6 +4860,9 @@
       <c r="J35" t="n">
         <v>57.7</v>
       </c>
+      <c r="K35" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4515,6 +4897,9 @@
       <c r="J36" t="n">
         <v>76.40000000000001</v>
       </c>
+      <c r="K36" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4549,6 +4934,9 @@
       <c r="J37" t="n">
         <v>77.3</v>
       </c>
+      <c r="K37" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4583,6 +4971,9 @@
       <c r="J38" t="n">
         <v>58.5</v>
       </c>
+      <c r="K38" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4617,6 +5008,9 @@
       <c r="J39" t="n">
         <v>47.9</v>
       </c>
+      <c r="K39" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4651,6 +5045,9 @@
       <c r="J40" t="n">
         <v>68.90000000000001</v>
       </c>
+      <c r="K40" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4685,6 +5082,9 @@
       <c r="J41" t="n">
         <v>91.59999999999999</v>
       </c>
+      <c r="K41" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4719,6 +5119,9 @@
       <c r="J42" t="n">
         <v>72.2</v>
       </c>
+      <c r="K42" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4753,6 +5156,9 @@
       <c r="J43" t="n">
         <v>54</v>
       </c>
+      <c r="K43" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4787,6 +5193,9 @@
       <c r="J44" t="n">
         <v>94.59999999999999</v>
       </c>
+      <c r="K44" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4821,6 +5230,9 @@
       <c r="J45" t="n">
         <v>93.2</v>
       </c>
+      <c r="K45" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4855,6 +5267,9 @@
       <c r="J46" t="n">
         <v>49.3</v>
       </c>
+      <c r="K46" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4889,6 +5304,9 @@
       <c r="J47" t="n">
         <v>66.59999999999999</v>
       </c>
+      <c r="K47" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4923,6 +5341,9 @@
       <c r="J48" t="n">
         <v>63.9</v>
       </c>
+      <c r="K48" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4957,6 +5378,9 @@
       <c r="J49" t="n">
         <v>41.3</v>
       </c>
+      <c r="K49" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4991,6 +5415,9 @@
       <c r="J50" t="n">
         <v>53</v>
       </c>
+      <c r="K50" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5025,6 +5452,9 @@
       <c r="J51" t="n">
         <v>47.8</v>
       </c>
+      <c r="K51" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5059,6 +5489,9 @@
       <c r="J52" t="n">
         <v>59.4</v>
       </c>
+      <c r="K52" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5093,6 +5526,9 @@
       <c r="J53" t="n">
         <v>70.8</v>
       </c>
+      <c r="K53" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5127,6 +5563,9 @@
       <c r="J54" t="n">
         <v>67.5</v>
       </c>
+      <c r="K54" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5161,6 +5600,9 @@
       <c r="J55" t="n">
         <v>44.4</v>
       </c>
+      <c r="K55" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5195,6 +5637,9 @@
       <c r="J56" t="n">
         <v>99.7</v>
       </c>
+      <c r="K56" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5229,6 +5674,9 @@
       <c r="J57" t="n">
         <v>86.09999999999999</v>
       </c>
+      <c r="K57" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5263,6 +5711,9 @@
       <c r="J58" t="n">
         <v>45.7</v>
       </c>
+      <c r="K58" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5297,6 +5748,9 @@
       <c r="J59" t="n">
         <v>45.6</v>
       </c>
+      <c r="K59" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5331,6 +5785,9 @@
       <c r="J60" t="n">
         <v>47.3</v>
       </c>
+      <c r="K60" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5365,6 +5822,9 @@
       <c r="J61" t="n">
         <v>61.1</v>
       </c>
+      <c r="K61" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5399,6 +5859,9 @@
       <c r="J62" t="n">
         <v>85.8</v>
       </c>
+      <c r="K62" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5433,6 +5896,9 @@
       <c r="J63" t="n">
         <v>41.6</v>
       </c>
+      <c r="K63" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5467,6 +5933,9 @@
       <c r="J64" t="n">
         <v>40.4</v>
       </c>
+      <c r="K64" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5501,6 +5970,9 @@
       <c r="J65" t="n">
         <v>52.9</v>
       </c>
+      <c r="K65" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5535,6 +6007,9 @@
       <c r="J66" t="n">
         <v>43.2</v>
       </c>
+      <c r="K66" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5569,6 +6044,9 @@
       <c r="J67" t="n">
         <v>56.4</v>
       </c>
+      <c r="K67" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5603,6 +6081,9 @@
       <c r="J68" t="n">
         <v>42.7</v>
       </c>
+      <c r="K68" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5637,6 +6118,9 @@
       <c r="J69" t="n">
         <v>59.7</v>
       </c>
+      <c r="K69" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5671,6 +6155,9 @@
       <c r="J70" t="n">
         <v>88.40000000000001</v>
       </c>
+      <c r="K70" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5705,6 +6192,9 @@
       <c r="J71" t="n">
         <v>74.40000000000001</v>
       </c>
+      <c r="K71" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5739,6 +6229,9 @@
       <c r="J72" t="n">
         <v>89.90000000000001</v>
       </c>
+      <c r="K72" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5773,6 +6266,9 @@
       <c r="J73" t="n">
         <v>58.6</v>
       </c>
+      <c r="K73" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5807,6 +6303,9 @@
       <c r="J74" t="n">
         <v>61</v>
       </c>
+      <c r="K74" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5841,6 +6340,9 @@
       <c r="J75" t="n">
         <v>85.59999999999999</v>
       </c>
+      <c r="K75" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5875,6 +6377,9 @@
       <c r="J76" t="n">
         <v>95.40000000000001</v>
       </c>
+      <c r="K76" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5909,6 +6414,9 @@
       <c r="J77" t="n">
         <v>66.5</v>
       </c>
+      <c r="K77" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5943,6 +6451,9 @@
       <c r="J78" t="n">
         <v>89.90000000000001</v>
       </c>
+      <c r="K78" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5977,6 +6488,9 @@
       <c r="J79" t="n">
         <v>87.5</v>
       </c>
+      <c r="K79" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6011,6 +6525,9 @@
       <c r="J80" t="n">
         <v>43.7</v>
       </c>
+      <c r="K80" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6045,6 +6562,9 @@
       <c r="J81" t="n">
         <v>66.3</v>
       </c>
+      <c r="K81" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6079,6 +6599,9 @@
       <c r="J82" t="n">
         <v>75.90000000000001</v>
       </c>
+      <c r="K82" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6113,6 +6636,9 @@
       <c r="J83" t="n">
         <v>79.40000000000001</v>
       </c>
+      <c r="K83" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6147,6 +6673,9 @@
       <c r="J84" t="n">
         <v>81.90000000000001</v>
       </c>
+      <c r="K84" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6181,6 +6710,9 @@
       <c r="J85" t="n">
         <v>80.2</v>
       </c>
+      <c r="K85" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6215,6 +6747,9 @@
       <c r="J86" t="n">
         <v>61.8</v>
       </c>
+      <c r="K86" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6249,6 +6784,9 @@
       <c r="J87" t="n">
         <v>90.7</v>
       </c>
+      <c r="K87" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6283,6 +6821,9 @@
       <c r="J88" t="n">
         <v>47.9</v>
       </c>
+      <c r="K88" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6317,6 +6858,9 @@
       <c r="J89" t="n">
         <v>64.7</v>
       </c>
+      <c r="K89" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6351,6 +6895,9 @@
       <c r="J90" t="n">
         <v>58.6</v>
       </c>
+      <c r="K90" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6385,12 +6932,13 @@
       <c r="J91" t="n">
         <v>56.9</v>
       </c>
+      <c r="K91" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>22099</t>
-        </is>
+      <c r="A92" t="n">
+        <v>22099</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -6420,6 +6968,9 @@
       </c>
       <c r="J92" t="n">
         <v>76</v>
+      </c>
+      <c r="K92" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -6433,7 +6984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6482,6 +7033,11 @@
           <t>Final Exam</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Assessments Completed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -6513,6 +7069,9 @@
       <c r="I2" t="n">
         <v>55</v>
       </c>
+      <c r="J2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -6544,6 +7103,9 @@
       <c r="I3" t="n">
         <v>57.1</v>
       </c>
+      <c r="J3" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6575,6 +7137,9 @@
       <c r="I4" t="n">
         <v>53.3</v>
       </c>
+      <c r="J4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -6606,6 +7171,9 @@
       <c r="I5" t="n">
         <v>99.7</v>
       </c>
+      <c r="J5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -6637,6 +7205,9 @@
       <c r="I6" t="n">
         <v>48.3</v>
       </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -6668,6 +7239,9 @@
       <c r="I7" t="n">
         <v>40.3</v>
       </c>
+      <c r="J7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -6699,6 +7273,9 @@
       <c r="I8" t="n">
         <v>46.7</v>
       </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -6730,6 +7307,9 @@
       <c r="I9" t="n">
         <v>46.7</v>
       </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6761,6 +7341,9 @@
       <c r="I10" t="n">
         <v>65.8</v>
       </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6792,6 +7375,9 @@
       <c r="I11" t="n">
         <v>44.1</v>
       </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6823,6 +7409,9 @@
       <c r="I12" t="n">
         <v>78.09999999999999</v>
       </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6854,6 +7443,9 @@
       <c r="I13" t="n">
         <v>77.7</v>
       </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6885,6 +7477,9 @@
       <c r="I14" t="n">
         <v>50.5</v>
       </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6916,6 +7511,9 @@
       <c r="I15" t="n">
         <v>86.59999999999999</v>
       </c>
+      <c r="J15" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6947,6 +7545,9 @@
       <c r="I16" t="n">
         <v>70.90000000000001</v>
       </c>
+      <c r="J16" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6978,6 +7579,9 @@
       <c r="I17" t="n">
         <v>86.90000000000001</v>
       </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7009,6 +7613,9 @@
       <c r="I18" t="n">
         <v>93.7</v>
       </c>
+      <c r="J18" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7040,6 +7647,9 @@
       <c r="I19" t="n">
         <v>88.09999999999999</v>
       </c>
+      <c r="J19" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7071,6 +7681,9 @@
       <c r="I20" t="n">
         <v>44.8</v>
       </c>
+      <c r="J20" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7102,6 +7715,9 @@
       <c r="I21" t="n">
         <v>42.5</v>
       </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7133,6 +7749,9 @@
       <c r="I22" t="n">
         <v>44.5</v>
       </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7164,6 +7783,9 @@
       <c r="I23" t="n">
         <v>76.5</v>
       </c>
+      <c r="J23" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7195,6 +7817,9 @@
       <c r="I24" t="n">
         <v>74</v>
       </c>
+      <c r="J24" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -7226,6 +7851,9 @@
       <c r="I25" t="n">
         <v>71.8</v>
       </c>
+      <c r="J25" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -7257,6 +7885,9 @@
       <c r="I26" t="n">
         <v>63.2</v>
       </c>
+      <c r="J26" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -7288,6 +7919,9 @@
       <c r="I27" t="n">
         <v>95</v>
       </c>
+      <c r="J27" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -7319,6 +7953,9 @@
       <c r="I28" t="n">
         <v>45.3</v>
       </c>
+      <c r="J28" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -7350,6 +7987,9 @@
       <c r="I29" t="n">
         <v>93.5</v>
       </c>
+      <c r="J29" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -7381,6 +8021,9 @@
       <c r="I30" t="n">
         <v>47.3</v>
       </c>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -7412,6 +8055,9 @@
       <c r="I31" t="n">
         <v>88.2</v>
       </c>
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -7443,6 +8089,9 @@
       <c r="I32" t="n">
         <v>71.5</v>
       </c>
+      <c r="J32" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -7474,6 +8123,9 @@
       <c r="I33" t="n">
         <v>80.8</v>
       </c>
+      <c r="J33" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -7505,6 +8157,9 @@
       <c r="I34" t="n">
         <v>66</v>
       </c>
+      <c r="J34" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -7536,6 +8191,9 @@
       <c r="I35" t="n">
         <v>82.59999999999999</v>
       </c>
+      <c r="J35" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -7567,6 +8225,9 @@
       <c r="I36" t="n">
         <v>73.09999999999999</v>
       </c>
+      <c r="J36" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -7598,6 +8259,9 @@
       <c r="I37" t="n">
         <v>49.3</v>
       </c>
+      <c r="J37" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -7629,6 +8293,9 @@
       <c r="I38" t="n">
         <v>41.7</v>
       </c>
+      <c r="J38" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -7660,6 +8327,9 @@
       <c r="I39" t="n">
         <v>78.3</v>
       </c>
+      <c r="J39" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -7691,6 +8361,9 @@
       <c r="I40" t="n">
         <v>81.09999999999999</v>
       </c>
+      <c r="J40" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -7722,6 +8395,9 @@
       <c r="I41" t="n">
         <v>76.40000000000001</v>
       </c>
+      <c r="J41" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -7753,6 +8429,9 @@
       <c r="I42" t="n">
         <v>62.2</v>
       </c>
+      <c r="J42" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -7784,6 +8463,9 @@
       <c r="I43" t="n">
         <v>57.4</v>
       </c>
+      <c r="J43" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -7815,6 +8497,9 @@
       <c r="I44" t="n">
         <v>74.7</v>
       </c>
+      <c r="J44" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -7846,6 +8531,9 @@
       <c r="I45" t="n">
         <v>41.4</v>
       </c>
+      <c r="J45" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -7877,6 +8565,9 @@
       <c r="I46" t="n">
         <v>69.7</v>
       </c>
+      <c r="J46" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7908,6 +8599,9 @@
       <c r="I47" t="n">
         <v>92.90000000000001</v>
       </c>
+      <c r="J47" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7939,6 +8633,9 @@
       <c r="I48" t="n">
         <v>73.2</v>
       </c>
+      <c r="J48" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7970,6 +8667,9 @@
       <c r="I49" t="n">
         <v>47.1</v>
       </c>
+      <c r="J49" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -8001,6 +8701,9 @@
       <c r="I50" t="n">
         <v>51.9</v>
       </c>
+      <c r="J50" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -8032,6 +8735,9 @@
       <c r="I51" t="n">
         <v>67.40000000000001</v>
       </c>
+      <c r="J51" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -8063,6 +8769,9 @@
       <c r="I52" t="n">
         <v>84.40000000000001</v>
       </c>
+      <c r="J52" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -8094,6 +8803,9 @@
       <c r="I53" t="n">
         <v>88.90000000000001</v>
       </c>
+      <c r="J53" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8125,6 +8837,9 @@
       <c r="I54" t="n">
         <v>81.3</v>
       </c>
+      <c r="J54" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8156,6 +8871,9 @@
       <c r="I55" t="n">
         <v>83.3</v>
       </c>
+      <c r="J55" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8187,6 +8905,9 @@
       <c r="I56" t="n">
         <v>80.8</v>
       </c>
+      <c r="J56" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8218,6 +8939,9 @@
       <c r="I57" t="n">
         <v>81.40000000000001</v>
       </c>
+      <c r="J57" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8249,6 +8973,9 @@
       <c r="I58" t="n">
         <v>48.3</v>
       </c>
+      <c r="J58" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8280,6 +9007,9 @@
       <c r="I59" t="n">
         <v>94.7</v>
       </c>
+      <c r="J59" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8311,6 +9041,9 @@
       <c r="I60" t="n">
         <v>76.59999999999999</v>
       </c>
+      <c r="J60" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8342,6 +9075,9 @@
       <c r="I61" t="n">
         <v>57.3</v>
       </c>
+      <c r="J61" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8373,6 +9109,9 @@
       <c r="I62" t="n">
         <v>56.4</v>
       </c>
+      <c r="J62" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8404,6 +9143,9 @@
       <c r="I63" t="n">
         <v>88.3</v>
       </c>
+      <c r="J63" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8435,6 +9177,9 @@
       <c r="I64" t="n">
         <v>68.7</v>
       </c>
+      <c r="J64" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8466,6 +9211,9 @@
       <c r="I65" t="n">
         <v>75.2</v>
       </c>
+      <c r="J65" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8497,6 +9245,9 @@
       <c r="I66" t="n">
         <v>83</v>
       </c>
+      <c r="J66" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8528,6 +9279,9 @@
       <c r="I67" t="n">
         <v>96.09999999999999</v>
       </c>
+      <c r="J67" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8559,6 +9313,9 @@
       <c r="I68" t="n">
         <v>94.5</v>
       </c>
+      <c r="J68" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8590,6 +9347,9 @@
       <c r="I69" t="n">
         <v>50.5</v>
       </c>
+      <c r="J69" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8621,6 +9381,9 @@
       <c r="I70" t="n">
         <v>96.2</v>
       </c>
+      <c r="J70" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8652,6 +9415,9 @@
       <c r="I71" t="n">
         <v>99</v>
       </c>
+      <c r="J71" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8683,6 +9449,9 @@
       <c r="I72" t="n">
         <v>68.09999999999999</v>
       </c>
+      <c r="J72" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8714,6 +9483,9 @@
       <c r="I73" t="n">
         <v>84.2</v>
       </c>
+      <c r="J73" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8745,6 +9517,9 @@
       <c r="I74" t="n">
         <v>89.59999999999999</v>
       </c>
+      <c r="J74" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8776,6 +9551,9 @@
       <c r="I75" t="n">
         <v>54.9</v>
       </c>
+      <c r="J75" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8807,6 +9585,9 @@
       <c r="I76" t="n">
         <v>40.7</v>
       </c>
+      <c r="J76" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8838,6 +9619,9 @@
       <c r="I77" t="n">
         <v>70.2</v>
       </c>
+      <c r="J77" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8869,6 +9653,9 @@
       <c r="I78" t="n">
         <v>76.90000000000001</v>
       </c>
+      <c r="J78" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8900,6 +9687,9 @@
       <c r="I79" t="n">
         <v>73</v>
       </c>
+      <c r="J79" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8931,6 +9721,9 @@
       <c r="I80" t="n">
         <v>92.40000000000001</v>
       </c>
+      <c r="J80" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8962,6 +9755,9 @@
       <c r="I81" t="n">
         <v>72.90000000000001</v>
       </c>
+      <c r="J81" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8993,6 +9789,9 @@
       <c r="I82" t="n">
         <v>52.3</v>
       </c>
+      <c r="J82" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9024,6 +9823,9 @@
       <c r="I83" t="n">
         <v>67.40000000000001</v>
       </c>
+      <c r="J83" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9055,6 +9857,9 @@
       <c r="I84" t="n">
         <v>84.7</v>
       </c>
+      <c r="J84" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9086,6 +9891,9 @@
       <c r="I85" t="n">
         <v>44.1</v>
       </c>
+      <c r="J85" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9117,6 +9925,9 @@
       <c r="I86" t="n">
         <v>78.8</v>
       </c>
+      <c r="J86" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9148,6 +9959,9 @@
       <c r="I87" t="n">
         <v>81</v>
       </c>
+      <c r="J87" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9179,6 +9993,9 @@
       <c r="I88" t="n">
         <v>71.7</v>
       </c>
+      <c r="J88" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9210,6 +10027,9 @@
       <c r="I89" t="n">
         <v>72.7</v>
       </c>
+      <c r="J89" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9241,6 +10061,9 @@
       <c r="I90" t="n">
         <v>83.5</v>
       </c>
+      <c r="J90" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9271,6 +10094,9 @@
       </c>
       <c r="I91" t="n">
         <v>52.4</v>
+      </c>
+      <c r="J91" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -9284,7 +10110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9338,6 +10164,11 @@
           <t>Final Exam</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Assessments Completed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -9372,6 +10203,9 @@
       <c r="J2" t="n">
         <v>54.1</v>
       </c>
+      <c r="K2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -9406,6 +10240,9 @@
       <c r="J3" t="n">
         <v>59.1</v>
       </c>
+      <c r="K3" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9440,6 +10277,9 @@
       <c r="J4" t="n">
         <v>58</v>
       </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -9474,6 +10314,9 @@
       <c r="J5" t="n">
         <v>98.3</v>
       </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -9508,6 +10351,9 @@
       <c r="J6" t="n">
         <v>85.3</v>
       </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -9542,6 +10388,9 @@
       <c r="J7" t="n">
         <v>98.09999999999999</v>
       </c>
+      <c r="K7" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -9576,6 +10425,9 @@
       <c r="J8" t="n">
         <v>45.5</v>
       </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -9610,6 +10462,9 @@
       <c r="J9" t="n">
         <v>85.7</v>
       </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9644,6 +10499,9 @@
       <c r="J10" t="n">
         <v>96.2</v>
       </c>
+      <c r="K10" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9678,6 +10536,9 @@
       <c r="J11" t="n">
         <v>94.90000000000001</v>
       </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9712,6 +10573,9 @@
       <c r="J12" t="n">
         <v>69.8</v>
       </c>
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9746,6 +10610,9 @@
       <c r="J13" t="n">
         <v>73.8</v>
       </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9780,6 +10647,9 @@
       <c r="J14" t="n">
         <v>59.8</v>
       </c>
+      <c r="K14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9814,6 +10684,9 @@
       <c r="J15" t="n">
         <v>98</v>
       </c>
+      <c r="K15" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9848,6 +10721,9 @@
       <c r="J16" t="n">
         <v>95</v>
       </c>
+      <c r="K16" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9882,6 +10758,9 @@
       <c r="J17" t="n">
         <v>85.90000000000001</v>
       </c>
+      <c r="K17" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9916,6 +10795,9 @@
       <c r="J18" t="n">
         <v>77.09999999999999</v>
       </c>
+      <c r="K18" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9950,6 +10832,9 @@
       <c r="J19" t="n">
         <v>71.8</v>
       </c>
+      <c r="K19" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9984,6 +10869,9 @@
       <c r="J20" t="n">
         <v>46.4</v>
       </c>
+      <c r="K20" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10018,6 +10906,9 @@
       <c r="J21" t="n">
         <v>62.4</v>
       </c>
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10052,6 +10943,9 @@
       <c r="J22" t="n">
         <v>91.5</v>
       </c>
+      <c r="K22" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10086,6 +10980,9 @@
       <c r="J23" t="n">
         <v>70</v>
       </c>
+      <c r="K23" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10120,6 +11017,9 @@
       <c r="J24" t="n">
         <v>52.7</v>
       </c>
+      <c r="K24" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -10154,6 +11054,9 @@
       <c r="J25" t="n">
         <v>73.8</v>
       </c>
+      <c r="K25" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -10188,6 +11091,9 @@
       <c r="J26" t="n">
         <v>63.9</v>
       </c>
+      <c r="K26" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -10222,6 +11128,9 @@
       <c r="J27" t="n">
         <v>85.3</v>
       </c>
+      <c r="K27" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -10256,6 +11165,9 @@
       <c r="J28" t="n">
         <v>90.3</v>
       </c>
+      <c r="K28" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -10290,6 +11202,9 @@
       <c r="J29" t="n">
         <v>99.59999999999999</v>
       </c>
+      <c r="K29" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -10324,6 +11239,9 @@
       <c r="J30" t="n">
         <v>77.09999999999999</v>
       </c>
+      <c r="K30" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -10358,6 +11276,9 @@
       <c r="J31" t="n">
         <v>59</v>
       </c>
+      <c r="K31" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -10392,6 +11313,9 @@
       <c r="J32" t="n">
         <v>66.90000000000001</v>
       </c>
+      <c r="K32" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -10426,6 +11350,9 @@
       <c r="J33" t="n">
         <v>63.1</v>
       </c>
+      <c r="K33" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -10460,6 +11387,9 @@
       <c r="J34" t="n">
         <v>50.2</v>
       </c>
+      <c r="K34" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -10494,6 +11424,9 @@
       <c r="J35" t="n">
         <v>69.09999999999999</v>
       </c>
+      <c r="K35" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -10528,6 +11461,9 @@
       <c r="J36" t="n">
         <v>58.3</v>
       </c>
+      <c r="K36" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -10562,6 +11498,9 @@
       <c r="J37" t="n">
         <v>91.59999999999999</v>
       </c>
+      <c r="K37" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -10596,6 +11535,9 @@
       <c r="J38" t="n">
         <v>98.09999999999999</v>
       </c>
+      <c r="K38" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -10630,6 +11572,9 @@
       <c r="J39" t="n">
         <v>63.6</v>
       </c>
+      <c r="K39" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -10664,6 +11609,9 @@
       <c r="J40" t="n">
         <v>67.7</v>
       </c>
+      <c r="K40" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -10698,6 +11646,9 @@
       <c r="J41" t="n">
         <v>70</v>
       </c>
+      <c r="K41" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -10732,6 +11683,9 @@
       <c r="J42" t="n">
         <v>68.8</v>
       </c>
+      <c r="K42" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -10766,6 +11720,9 @@
       <c r="J43" t="n">
         <v>93.7</v>
       </c>
+      <c r="K43" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -10800,6 +11757,9 @@
       <c r="J44" t="n">
         <v>42.7</v>
       </c>
+      <c r="K44" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -10834,6 +11794,9 @@
       <c r="J45" t="n">
         <v>55.5</v>
       </c>
+      <c r="K45" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -10868,6 +11831,9 @@
       <c r="J46" t="n">
         <v>75.3</v>
       </c>
+      <c r="K46" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -10902,6 +11868,9 @@
       <c r="J47" t="n">
         <v>96.40000000000001</v>
       </c>
+      <c r="K47" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -10936,6 +11905,9 @@
       <c r="J48" t="n">
         <v>81.8</v>
       </c>
+      <c r="K48" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -10970,6 +11942,9 @@
       <c r="J49" t="n">
         <v>49.9</v>
       </c>
+      <c r="K49" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -11004,6 +11979,9 @@
       <c r="J50" t="n">
         <v>64.3</v>
       </c>
+      <c r="K50" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -11038,6 +12016,9 @@
       <c r="J51" t="n">
         <v>63.3</v>
       </c>
+      <c r="K51" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -11072,6 +12053,9 @@
       <c r="J52" t="n">
         <v>51.2</v>
       </c>
+      <c r="K52" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -11106,6 +12090,9 @@
       <c r="J53" t="n">
         <v>76.7</v>
       </c>
+      <c r="K53" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -11140,6 +12127,9 @@
       <c r="J54" t="n">
         <v>76.90000000000001</v>
       </c>
+      <c r="K54" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -11174,6 +12164,9 @@
       <c r="J55" t="n">
         <v>65.09999999999999</v>
       </c>
+      <c r="K55" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -11208,6 +12201,9 @@
       <c r="J56" t="n">
         <v>73.3</v>
       </c>
+      <c r="K56" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -11242,6 +12238,9 @@
       <c r="J57" t="n">
         <v>48.2</v>
       </c>
+      <c r="K57" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -11276,6 +12275,9 @@
       <c r="J58" t="n">
         <v>69.3</v>
       </c>
+      <c r="K58" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -11310,6 +12312,9 @@
       <c r="J59" t="n">
         <v>67.40000000000001</v>
       </c>
+      <c r="K59" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -11344,6 +12349,9 @@
       <c r="J60" t="n">
         <v>62</v>
       </c>
+      <c r="K60" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -11378,6 +12386,9 @@
       <c r="J61" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="K61" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -11412,6 +12423,9 @@
       <c r="J62" t="n">
         <v>86.5</v>
       </c>
+      <c r="K62" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -11446,6 +12460,9 @@
       <c r="J63" t="n">
         <v>48.4</v>
       </c>
+      <c r="K63" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -11480,6 +12497,9 @@
       <c r="J64" t="n">
         <v>82.2</v>
       </c>
+      <c r="K64" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -11514,6 +12534,9 @@
       <c r="J65" t="n">
         <v>87.09999999999999</v>
       </c>
+      <c r="K65" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -11548,6 +12571,9 @@
       <c r="J66" t="n">
         <v>89.7</v>
       </c>
+      <c r="K66" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -11582,6 +12608,9 @@
       <c r="J67" t="n">
         <v>78</v>
       </c>
+      <c r="K67" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -11616,6 +12645,9 @@
       <c r="J68" t="n">
         <v>59.6</v>
       </c>
+      <c r="K68" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -11650,6 +12682,9 @@
       <c r="J69" t="n">
         <v>43.8</v>
       </c>
+      <c r="K69" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -11684,6 +12719,9 @@
       <c r="J70" t="n">
         <v>74.7</v>
       </c>
+      <c r="K70" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -11718,6 +12756,9 @@
       <c r="J71" t="n">
         <v>67.59999999999999</v>
       </c>
+      <c r="K71" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -11752,6 +12793,9 @@
       <c r="J72" t="n">
         <v>47.9</v>
       </c>
+      <c r="K72" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -11786,6 +12830,9 @@
       <c r="J73" t="n">
         <v>94.2</v>
       </c>
+      <c r="K73" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -11820,6 +12867,9 @@
       <c r="J74" t="n">
         <v>40.1</v>
       </c>
+      <c r="K74" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -11854,6 +12904,9 @@
       <c r="J75" t="n">
         <v>99.3</v>
       </c>
+      <c r="K75" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -11888,6 +12941,9 @@
       <c r="J76" t="n">
         <v>92.90000000000001</v>
       </c>
+      <c r="K76" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -11922,6 +12978,9 @@
       <c r="J77" t="n">
         <v>40.5</v>
       </c>
+      <c r="K77" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -11956,6 +13015,9 @@
       <c r="J78" t="n">
         <v>91.59999999999999</v>
       </c>
+      <c r="K78" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -11990,6 +13052,9 @@
       <c r="J79" t="n">
         <v>48.4</v>
       </c>
+      <c r="K79" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -12024,6 +13089,9 @@
       <c r="J80" t="n">
         <v>90.90000000000001</v>
       </c>
+      <c r="K80" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -12058,6 +13126,9 @@
       <c r="J81" t="n">
         <v>93.90000000000001</v>
       </c>
+      <c r="K81" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -12092,6 +13163,9 @@
       <c r="J82" t="n">
         <v>99.2</v>
       </c>
+      <c r="K82" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -12126,6 +13200,9 @@
       <c r="J83" t="n">
         <v>97.3</v>
       </c>
+      <c r="K83" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -12160,6 +13237,9 @@
       <c r="J84" t="n">
         <v>70.40000000000001</v>
       </c>
+      <c r="K84" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -12194,6 +13274,9 @@
       <c r="J85" t="n">
         <v>56.6</v>
       </c>
+      <c r="K85" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -12228,6 +13311,9 @@
       <c r="J86" t="n">
         <v>90.09999999999999</v>
       </c>
+      <c r="K86" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -12262,6 +13348,9 @@
       <c r="J87" t="n">
         <v>66.09999999999999</v>
       </c>
+      <c r="K87" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12296,6 +13385,9 @@
       <c r="J88" t="n">
         <v>82.09999999999999</v>
       </c>
+      <c r="K88" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12330,6 +13422,9 @@
       <c r="J89" t="n">
         <v>86.90000000000001</v>
       </c>
+      <c r="K89" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -12364,6 +13459,9 @@
       <c r="J90" t="n">
         <v>82.7</v>
       </c>
+      <c r="K90" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -12397,6 +13495,9 @@
       </c>
       <c r="J91" t="n">
         <v>55.3</v>
+      </c>
+      <c r="K91" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -12410,7 +13511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12459,6 +13560,11 @@
           <t>Final Exam</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Assessments Completed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -12490,6 +13596,9 @@
       <c r="I2" t="n">
         <v>91.8</v>
       </c>
+      <c r="J2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -12521,6 +13630,9 @@
       <c r="I3" t="n">
         <v>73.2</v>
       </c>
+      <c r="J3" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12552,6 +13664,9 @@
       <c r="I4" t="n">
         <v>56.3</v>
       </c>
+      <c r="J4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -12583,6 +13698,9 @@
       <c r="I5" t="n">
         <v>98.90000000000001</v>
       </c>
+      <c r="J5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -12614,6 +13732,9 @@
       <c r="I6" t="n">
         <v>73.2</v>
       </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -12645,6 +13766,9 @@
       <c r="I7" t="n">
         <v>75.5</v>
       </c>
+      <c r="J7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -12676,6 +13800,9 @@
       <c r="I8" t="n">
         <v>40.4</v>
       </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -12707,6 +13834,9 @@
       <c r="I9" t="n">
         <v>40.1</v>
       </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -12738,6 +13868,9 @@
       <c r="I10" t="n">
         <v>69.5</v>
       </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -12769,6 +13902,9 @@
       <c r="I11" t="n">
         <v>71.2</v>
       </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -12800,6 +13936,9 @@
       <c r="I12" t="n">
         <v>89.2</v>
       </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -12831,6 +13970,9 @@
       <c r="I13" t="n">
         <v>58.9</v>
       </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -12862,6 +14004,9 @@
       <c r="I14" t="n">
         <v>52.2</v>
       </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -12893,6 +14038,9 @@
       <c r="I15" t="n">
         <v>72.2</v>
       </c>
+      <c r="J15" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -12924,6 +14072,9 @@
       <c r="I16" t="n">
         <v>81.2</v>
       </c>
+      <c r="J16" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -12955,6 +14106,9 @@
       <c r="I17" t="n">
         <v>54.9</v>
       </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12986,6 +14140,9 @@
       <c r="I18" t="n">
         <v>64.3</v>
       </c>
+      <c r="J18" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -13017,6 +14174,9 @@
       <c r="I19" t="n">
         <v>40.7</v>
       </c>
+      <c r="J19" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -13048,6 +14208,9 @@
       <c r="I20" t="n">
         <v>78.7</v>
       </c>
+      <c r="J20" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -13079,6 +14242,9 @@
       <c r="I21" t="n">
         <v>66.59999999999999</v>
       </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -13110,6 +14276,9 @@
       <c r="I22" t="n">
         <v>50.1</v>
       </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -13141,6 +14310,9 @@
       <c r="I23" t="n">
         <v>52.9</v>
       </c>
+      <c r="J23" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -13172,6 +14344,9 @@
       <c r="I24" t="n">
         <v>57.7</v>
       </c>
+      <c r="J24" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -13203,6 +14378,9 @@
       <c r="I25" t="n">
         <v>93.09999999999999</v>
       </c>
+      <c r="J25" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -13234,6 +14412,9 @@
       <c r="I26" t="n">
         <v>61.5</v>
       </c>
+      <c r="J26" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -13265,6 +14446,9 @@
       <c r="I27" t="n">
         <v>59.1</v>
       </c>
+      <c r="J27" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -13296,6 +14480,9 @@
       <c r="I28" t="n">
         <v>86</v>
       </c>
+      <c r="J28" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -13327,6 +14514,9 @@
       <c r="I29" t="n">
         <v>95</v>
       </c>
+      <c r="J29" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -13358,6 +14548,9 @@
       <c r="I30" t="n">
         <v>90.40000000000001</v>
       </c>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -13389,6 +14582,9 @@
       <c r="I31" t="n">
         <v>41.7</v>
       </c>
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -13420,6 +14616,9 @@
       <c r="I32" t="n">
         <v>92.90000000000001</v>
       </c>
+      <c r="J32" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -13451,6 +14650,9 @@
       <c r="I33" t="n">
         <v>71.59999999999999</v>
       </c>
+      <c r="J33" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -13482,6 +14684,9 @@
       <c r="I34" t="n">
         <v>90.7</v>
       </c>
+      <c r="J34" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -13513,6 +14718,9 @@
       <c r="I35" t="n">
         <v>91.59999999999999</v>
       </c>
+      <c r="J35" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -13544,6 +14752,9 @@
       <c r="I36" t="n">
         <v>48.2</v>
       </c>
+      <c r="J36" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -13575,6 +14786,9 @@
       <c r="I37" t="n">
         <v>98.09999999999999</v>
       </c>
+      <c r="J37" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -13606,6 +14820,9 @@
       <c r="I38" t="n">
         <v>58.4</v>
       </c>
+      <c r="J38" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -13637,6 +14854,9 @@
       <c r="I39" t="n">
         <v>99.7</v>
       </c>
+      <c r="J39" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -13668,6 +14888,9 @@
       <c r="I40" t="n">
         <v>73.90000000000001</v>
       </c>
+      <c r="J40" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -13699,6 +14922,9 @@
       <c r="I41" t="n">
         <v>93.09999999999999</v>
       </c>
+      <c r="J41" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -13730,6 +14956,9 @@
       <c r="I42" t="n">
         <v>55</v>
       </c>
+      <c r="J42" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -13761,6 +14990,9 @@
       <c r="I43" t="n">
         <v>98.09999999999999</v>
       </c>
+      <c r="J43" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -13792,6 +15024,9 @@
       <c r="I44" t="n">
         <v>91.8</v>
       </c>
+      <c r="J44" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -13823,6 +15058,9 @@
       <c r="I45" t="n">
         <v>59.1</v>
       </c>
+      <c r="J45" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -13854,6 +15092,9 @@
       <c r="I46" t="n">
         <v>93.90000000000001</v>
       </c>
+      <c r="J46" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -13885,6 +15126,9 @@
       <c r="I47" t="n">
         <v>49.9</v>
       </c>
+      <c r="J47" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -13916,6 +15160,9 @@
       <c r="I48" t="n">
         <v>83.3</v>
       </c>
+      <c r="J48" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -13947,6 +15194,9 @@
       <c r="I49" t="n">
         <v>90.40000000000001</v>
       </c>
+      <c r="J49" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -13978,6 +15228,9 @@
       <c r="I50" t="n">
         <v>52</v>
       </c>
+      <c r="J50" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -14009,6 +15262,9 @@
       <c r="I51" t="n">
         <v>63.8</v>
       </c>
+      <c r="J51" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -14040,6 +15296,9 @@
       <c r="I52" t="n">
         <v>62.2</v>
       </c>
+      <c r="J52" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -14071,6 +15330,9 @@
       <c r="I53" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="J53" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -14102,6 +15364,9 @@
       <c r="I54" t="n">
         <v>73.2</v>
       </c>
+      <c r="J54" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -14133,6 +15398,9 @@
       <c r="I55" t="n">
         <v>92.90000000000001</v>
       </c>
+      <c r="J55" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -14164,6 +15432,9 @@
       <c r="I56" t="n">
         <v>88</v>
       </c>
+      <c r="J56" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -14195,6 +15466,9 @@
       <c r="I57" t="n">
         <v>98.3</v>
       </c>
+      <c r="J57" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -14226,6 +15500,9 @@
       <c r="I58" t="n">
         <v>77.59999999999999</v>
       </c>
+      <c r="J58" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -14257,6 +15534,9 @@
       <c r="I59" t="n">
         <v>63.8</v>
       </c>
+      <c r="J59" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -14288,6 +15568,9 @@
       <c r="I60" t="n">
         <v>71.40000000000001</v>
       </c>
+      <c r="J60" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -14319,6 +15602,9 @@
       <c r="I61" t="n">
         <v>95.5</v>
       </c>
+      <c r="J61" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -14350,6 +15636,9 @@
       <c r="I62" t="n">
         <v>63</v>
       </c>
+      <c r="J62" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -14381,6 +15670,9 @@
       <c r="I63" t="n">
         <v>81.59999999999999</v>
       </c>
+      <c r="J63" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -14412,6 +15704,9 @@
       <c r="I64" t="n">
         <v>93.8</v>
       </c>
+      <c r="J64" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -14443,6 +15738,9 @@
       <c r="I65" t="n">
         <v>45.9</v>
       </c>
+      <c r="J65" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -14474,6 +15772,9 @@
       <c r="I66" t="n">
         <v>65</v>
       </c>
+      <c r="J66" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -14505,6 +15806,9 @@
       <c r="I67" t="n">
         <v>92</v>
       </c>
+      <c r="J67" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -14536,6 +15840,9 @@
       <c r="I68" t="n">
         <v>91.09999999999999</v>
       </c>
+      <c r="J68" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -14567,6 +15874,9 @@
       <c r="I69" t="n">
         <v>67.40000000000001</v>
       </c>
+      <c r="J69" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -14598,6 +15908,9 @@
       <c r="I70" t="n">
         <v>47.4</v>
       </c>
+      <c r="J70" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -14629,6 +15942,9 @@
       <c r="I71" t="n">
         <v>61</v>
       </c>
+      <c r="J71" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -14660,6 +15976,9 @@
       <c r="I72" t="n">
         <v>49.8</v>
       </c>
+      <c r="J72" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -14691,6 +16010,9 @@
       <c r="I73" t="n">
         <v>64.59999999999999</v>
       </c>
+      <c r="J73" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -14722,6 +16044,9 @@
       <c r="I74" t="n">
         <v>76.09999999999999</v>
       </c>
+      <c r="J74" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -14753,6 +16078,9 @@
       <c r="I75" t="n">
         <v>65.40000000000001</v>
       </c>
+      <c r="J75" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -14784,6 +16112,9 @@
       <c r="I76" t="n">
         <v>63.8</v>
       </c>
+      <c r="J76" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -14815,6 +16146,9 @@
       <c r="I77" t="n">
         <v>76.5</v>
       </c>
+      <c r="J77" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -14846,6 +16180,9 @@
       <c r="I78" t="n">
         <v>55.7</v>
       </c>
+      <c r="J78" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -14877,6 +16214,9 @@
       <c r="I79" t="n">
         <v>88.3</v>
       </c>
+      <c r="J79" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -14908,6 +16248,9 @@
       <c r="I80" t="n">
         <v>99.8</v>
       </c>
+      <c r="J80" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -14939,6 +16282,9 @@
       <c r="I81" t="n">
         <v>51.4</v>
       </c>
+      <c r="J81" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -14970,6 +16316,9 @@
       <c r="I82" t="n">
         <v>70.40000000000001</v>
       </c>
+      <c r="J82" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -15001,6 +16350,9 @@
       <c r="I83" t="n">
         <v>55.5</v>
       </c>
+      <c r="J83" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -15032,6 +16384,9 @@
       <c r="I84" t="n">
         <v>61.3</v>
       </c>
+      <c r="J84" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -15063,6 +16418,9 @@
       <c r="I85" t="n">
         <v>91.09999999999999</v>
       </c>
+      <c r="J85" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -15094,6 +16452,9 @@
       <c r="I86" t="n">
         <v>70</v>
       </c>
+      <c r="J86" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -15125,6 +16486,9 @@
       <c r="I87" t="n">
         <v>52</v>
       </c>
+      <c r="J87" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -15156,6 +16520,9 @@
       <c r="I88" t="n">
         <v>86.7</v>
       </c>
+      <c r="J88" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -15187,6 +16554,9 @@
       <c r="I89" t="n">
         <v>85.7</v>
       </c>
+      <c r="J89" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -15218,6 +16588,9 @@
       <c r="I90" t="n">
         <v>78</v>
       </c>
+      <c r="J90" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -15248,6 +16621,9 @@
       </c>
       <c r="I91" t="n">
         <v>40.8</v>
+      </c>
+      <c r="J91" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -15261,7 +16637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15315,6 +16691,11 @@
           <t>Final Exam</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Assessments Completed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -15349,6 +16730,9 @@
       <c r="J2" t="n">
         <v>60.7</v>
       </c>
+      <c r="K2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -15383,6 +16767,9 @@
       <c r="J3" t="n">
         <v>83.7</v>
       </c>
+      <c r="K3" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15417,6 +16804,9 @@
       <c r="J4" t="n">
         <v>51.3</v>
       </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -15451,6 +16841,9 @@
       <c r="J5" t="n">
         <v>75.40000000000001</v>
       </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -15485,6 +16878,9 @@
       <c r="J6" t="n">
         <v>42.9</v>
       </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -15519,6 +16915,9 @@
       <c r="J7" t="n">
         <v>72.8</v>
       </c>
+      <c r="K7" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -15553,6 +16952,9 @@
       <c r="J8" t="n">
         <v>56.2</v>
       </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -15587,6 +16989,9 @@
       <c r="J9" t="n">
         <v>46.4</v>
       </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -15621,6 +17026,9 @@
       <c r="J10" t="n">
         <v>42.4</v>
       </c>
+      <c r="K10" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -15655,6 +17063,9 @@
       <c r="J11" t="n">
         <v>90.09999999999999</v>
       </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -15689,6 +17100,9 @@
       <c r="J12" t="n">
         <v>53.9</v>
       </c>
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15723,6 +17137,9 @@
       <c r="J13" t="n">
         <v>88.09999999999999</v>
       </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15757,6 +17174,9 @@
       <c r="J14" t="n">
         <v>50.2</v>
       </c>
+      <c r="K14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15791,6 +17211,9 @@
       <c r="J15" t="n">
         <v>64</v>
       </c>
+      <c r="K15" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15825,6 +17248,9 @@
       <c r="J16" t="n">
         <v>46.8</v>
       </c>
+      <c r="K16" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15859,6 +17285,9 @@
       <c r="J17" t="n">
         <v>80.7</v>
       </c>
+      <c r="K17" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15893,6 +17322,9 @@
       <c r="J18" t="n">
         <v>47.8</v>
       </c>
+      <c r="K18" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15927,6 +17359,9 @@
       <c r="J19" t="n">
         <v>80.7</v>
       </c>
+      <c r="K19" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15961,6 +17396,9 @@
       <c r="J20" t="n">
         <v>82</v>
       </c>
+      <c r="K20" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15995,6 +17433,9 @@
       <c r="J21" t="n">
         <v>73.5</v>
       </c>
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -16029,6 +17470,9 @@
       <c r="J22" t="n">
         <v>44.5</v>
       </c>
+      <c r="K22" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -16063,6 +17507,9 @@
       <c r="J23" t="n">
         <v>54.1</v>
       </c>
+      <c r="K23" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16097,6 +17544,9 @@
       <c r="J24" t="n">
         <v>79.2</v>
       </c>
+      <c r="K24" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -16131,6 +17581,9 @@
       <c r="J25" t="n">
         <v>58.3</v>
       </c>
+      <c r="K25" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -16165,6 +17618,9 @@
       <c r="J26" t="n">
         <v>67.3</v>
       </c>
+      <c r="K26" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -16199,6 +17655,9 @@
       <c r="J27" t="n">
         <v>53.3</v>
       </c>
+      <c r="K27" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -16233,6 +17692,9 @@
       <c r="J28" t="n">
         <v>49.8</v>
       </c>
+      <c r="K28" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -16267,6 +17729,9 @@
       <c r="J29" t="n">
         <v>63.6</v>
       </c>
+      <c r="K29" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -16301,6 +17766,9 @@
       <c r="J30" t="n">
         <v>75.3</v>
       </c>
+      <c r="K30" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -16335,6 +17803,9 @@
       <c r="J31" t="n">
         <v>42.9</v>
       </c>
+      <c r="K31" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -16369,6 +17840,9 @@
       <c r="J32" t="n">
         <v>83.8</v>
       </c>
+      <c r="K32" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -16403,6 +17877,9 @@
       <c r="J33" t="n">
         <v>95</v>
       </c>
+      <c r="K33" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -16437,6 +17914,9 @@
       <c r="J34" t="n">
         <v>82</v>
       </c>
+      <c r="K34" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -16471,6 +17951,9 @@
       <c r="J35" t="n">
         <v>52.1</v>
       </c>
+      <c r="K35" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -16505,6 +17988,9 @@
       <c r="J36" t="n">
         <v>70.2</v>
       </c>
+      <c r="K36" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -16539,6 +18025,9 @@
       <c r="J37" t="n">
         <v>65</v>
       </c>
+      <c r="K37" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -16573,6 +18062,9 @@
       <c r="J38" t="n">
         <v>48.7</v>
       </c>
+      <c r="K38" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -16607,6 +18099,9 @@
       <c r="J39" t="n">
         <v>81.40000000000001</v>
       </c>
+      <c r="K39" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -16641,6 +18136,9 @@
       <c r="J40" t="n">
         <v>91.90000000000001</v>
       </c>
+      <c r="K40" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -16675,6 +18173,9 @@
       <c r="J41" t="n">
         <v>95.59999999999999</v>
       </c>
+      <c r="K41" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -16709,6 +18210,9 @@
       <c r="J42" t="n">
         <v>77.2</v>
       </c>
+      <c r="K42" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -16743,6 +18247,9 @@
       <c r="J43" t="n">
         <v>72.8</v>
       </c>
+      <c r="K43" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -16777,6 +18284,9 @@
       <c r="J44" t="n">
         <v>50.4</v>
       </c>
+      <c r="K44" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -16811,6 +18321,9 @@
       <c r="J45" t="n">
         <v>59.8</v>
       </c>
+      <c r="K45" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -16845,6 +18358,9 @@
       <c r="J46" t="n">
         <v>79.7</v>
       </c>
+      <c r="K46" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -16879,6 +18395,9 @@
       <c r="J47" t="n">
         <v>44.1</v>
       </c>
+      <c r="K47" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -16913,6 +18432,9 @@
       <c r="J48" t="n">
         <v>61.6</v>
       </c>
+      <c r="K48" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -16947,6 +18469,9 @@
       <c r="J49" t="n">
         <v>80.09999999999999</v>
       </c>
+      <c r="K49" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -16981,6 +18506,9 @@
       <c r="J50" t="n">
         <v>95</v>
       </c>
+      <c r="K50" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -17015,6 +18543,9 @@
       <c r="J51" t="n">
         <v>88.2</v>
       </c>
+      <c r="K51" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -17049,6 +18580,9 @@
       <c r="J52" t="n">
         <v>97.40000000000001</v>
       </c>
+      <c r="K52" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -17083,6 +18617,9 @@
       <c r="J53" t="n">
         <v>46.2</v>
       </c>
+      <c r="K53" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -17117,6 +18654,9 @@
       <c r="J54" t="n">
         <v>49.2</v>
       </c>
+      <c r="K54" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -17151,6 +18691,9 @@
       <c r="J55" t="n">
         <v>53.7</v>
       </c>
+      <c r="K55" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -17185,6 +18728,9 @@
       <c r="J56" t="n">
         <v>78.5</v>
       </c>
+      <c r="K56" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -17219,6 +18765,9 @@
       <c r="J57" t="n">
         <v>87.2</v>
       </c>
+      <c r="K57" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -17253,6 +18802,9 @@
       <c r="J58" t="n">
         <v>72</v>
       </c>
+      <c r="K58" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -17287,6 +18839,9 @@
       <c r="J59" t="n">
         <v>94.90000000000001</v>
       </c>
+      <c r="K59" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -17321,6 +18876,9 @@
       <c r="J60" t="n">
         <v>40.3</v>
       </c>
+      <c r="K60" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -17355,6 +18913,9 @@
       <c r="J61" t="n">
         <v>64.8</v>
       </c>
+      <c r="K61" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -17389,6 +18950,9 @@
       <c r="J62" t="n">
         <v>88</v>
       </c>
+      <c r="K62" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -17423,6 +18987,9 @@
       <c r="J63" t="n">
         <v>44</v>
       </c>
+      <c r="K63" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -17457,6 +19024,9 @@
       <c r="J64" t="n">
         <v>77.2</v>
       </c>
+      <c r="K64" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -17491,6 +19061,9 @@
       <c r="J65" t="n">
         <v>61.9</v>
       </c>
+      <c r="K65" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -17525,6 +19098,9 @@
       <c r="J66" t="n">
         <v>90.40000000000001</v>
       </c>
+      <c r="K66" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -17559,6 +19135,9 @@
       <c r="J67" t="n">
         <v>50.5</v>
       </c>
+      <c r="K67" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -17593,6 +19172,9 @@
       <c r="J68" t="n">
         <v>44.6</v>
       </c>
+      <c r="K68" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -17627,6 +19209,9 @@
       <c r="J69" t="n">
         <v>94.40000000000001</v>
       </c>
+      <c r="K69" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -17661,6 +19246,9 @@
       <c r="J70" t="n">
         <v>86.3</v>
       </c>
+      <c r="K70" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -17695,6 +19283,9 @@
       <c r="J71" t="n">
         <v>90.90000000000001</v>
       </c>
+      <c r="K71" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -17729,6 +19320,9 @@
       <c r="J72" t="n">
         <v>79.59999999999999</v>
       </c>
+      <c r="K72" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -17763,6 +19357,9 @@
       <c r="J73" t="n">
         <v>62.2</v>
       </c>
+      <c r="K73" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -17797,6 +19394,9 @@
       <c r="J74" t="n">
         <v>98.8</v>
       </c>
+      <c r="K74" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -17831,6 +19431,9 @@
       <c r="J75" t="n">
         <v>50.4</v>
       </c>
+      <c r="K75" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -17865,6 +19468,9 @@
       <c r="J76" t="n">
         <v>71</v>
       </c>
+      <c r="K76" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -17899,6 +19505,9 @@
       <c r="J77" t="n">
         <v>49.9</v>
       </c>
+      <c r="K77" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -17933,6 +19542,9 @@
       <c r="J78" t="n">
         <v>53.8</v>
       </c>
+      <c r="K78" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -17967,6 +19579,9 @@
       <c r="J79" t="n">
         <v>41.3</v>
       </c>
+      <c r="K79" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -18001,6 +19616,9 @@
       <c r="J80" t="n">
         <v>55.5</v>
       </c>
+      <c r="K80" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -18035,6 +19653,9 @@
       <c r="J81" t="n">
         <v>57</v>
       </c>
+      <c r="K81" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -18069,6 +19690,9 @@
       <c r="J82" t="n">
         <v>87.7</v>
       </c>
+      <c r="K82" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -18103,6 +19727,9 @@
       <c r="J83" t="n">
         <v>75.40000000000001</v>
       </c>
+      <c r="K83" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -18137,6 +19764,9 @@
       <c r="J84" t="n">
         <v>49</v>
       </c>
+      <c r="K84" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -18171,6 +19801,9 @@
       <c r="J85" t="n">
         <v>68.90000000000001</v>
       </c>
+      <c r="K85" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -18205,6 +19838,9 @@
       <c r="J86" t="n">
         <v>62.2</v>
       </c>
+      <c r="K86" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -18239,6 +19875,9 @@
       <c r="J87" t="n">
         <v>84.5</v>
       </c>
+      <c r="K87" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -18273,6 +19912,9 @@
       <c r="J88" t="n">
         <v>57</v>
       </c>
+      <c r="K88" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -18307,6 +19949,9 @@
       <c r="J89" t="n">
         <v>40.4</v>
       </c>
+      <c r="K89" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -18341,6 +19986,9 @@
       <c r="J90" t="n">
         <v>91.3</v>
       </c>
+      <c r="K90" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -18374,6 +20022,9 @@
       </c>
       <c r="J91" t="n">
         <v>68.90000000000001</v>
+      </c>
+      <c r="K91" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -18387,7 +20038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18436,6 +20087,11 @@
           <t>Final Exam</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Assessments Completed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -18467,6 +20123,9 @@
       <c r="I2" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="J2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -18498,6 +20157,9 @@
       <c r="I3" t="n">
         <v>52.9</v>
       </c>
+      <c r="J3" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18529,6 +20191,9 @@
       <c r="I4" t="n">
         <v>97.90000000000001</v>
       </c>
+      <c r="J4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -18560,6 +20225,9 @@
       <c r="I5" t="n">
         <v>53.3</v>
       </c>
+      <c r="J5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -18591,6 +20259,9 @@
       <c r="I6" t="n">
         <v>82.7</v>
       </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -18622,6 +20293,9 @@
       <c r="I7" t="n">
         <v>79.40000000000001</v>
       </c>
+      <c r="J7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -18653,6 +20327,9 @@
       <c r="I8" t="n">
         <v>50.2</v>
       </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -18684,6 +20361,9 @@
       <c r="I9" t="n">
         <v>61.2</v>
       </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -18715,6 +20395,9 @@
       <c r="I10" t="n">
         <v>57.1</v>
       </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -18746,6 +20429,9 @@
       <c r="I11" t="n">
         <v>51.7</v>
       </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -18777,6 +20463,9 @@
       <c r="I12" t="n">
         <v>57.7</v>
       </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -18808,6 +20497,9 @@
       <c r="I13" t="n">
         <v>81.7</v>
       </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -18839,6 +20531,9 @@
       <c r="I14" t="n">
         <v>67.59999999999999</v>
       </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -18870,6 +20565,9 @@
       <c r="I15" t="n">
         <v>80.59999999999999</v>
       </c>
+      <c r="J15" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -18901,6 +20599,9 @@
       <c r="I16" t="n">
         <v>54.9</v>
       </c>
+      <c r="J16" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -18932,6 +20633,9 @@
       <c r="I17" t="n">
         <v>61.2</v>
       </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -18963,6 +20667,9 @@
       <c r="I18" t="n">
         <v>52</v>
       </c>
+      <c r="J18" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -18994,6 +20701,9 @@
       <c r="I19" t="n">
         <v>49.4</v>
       </c>
+      <c r="J19" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -19025,6 +20735,9 @@
       <c r="I20" t="n">
         <v>72.5</v>
       </c>
+      <c r="J20" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -19056,6 +20769,9 @@
       <c r="I21" t="n">
         <v>92.09999999999999</v>
       </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -19087,6 +20803,9 @@
       <c r="I22" t="n">
         <v>43.2</v>
       </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -19118,6 +20837,9 @@
       <c r="I23" t="n">
         <v>50.5</v>
       </c>
+      <c r="J23" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19149,6 +20871,9 @@
       <c r="I24" t="n">
         <v>74.90000000000001</v>
       </c>
+      <c r="J24" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -19180,6 +20905,9 @@
       <c r="I25" t="n">
         <v>76.8</v>
       </c>
+      <c r="J25" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -19211,6 +20939,9 @@
       <c r="I26" t="n">
         <v>56.8</v>
       </c>
+      <c r="J26" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -19242,6 +20973,9 @@
       <c r="I27" t="n">
         <v>54.1</v>
       </c>
+      <c r="J27" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -19273,6 +21007,9 @@
       <c r="I28" t="n">
         <v>50.6</v>
       </c>
+      <c r="J28" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -19304,6 +21041,9 @@
       <c r="I29" t="n">
         <v>58</v>
       </c>
+      <c r="J29" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -19335,6 +21075,9 @@
       <c r="I30" t="n">
         <v>68.59999999999999</v>
       </c>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -19366,6 +21109,9 @@
       <c r="I31" t="n">
         <v>55.5</v>
       </c>
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -19397,6 +21143,9 @@
       <c r="I32" t="n">
         <v>78.90000000000001</v>
       </c>
+      <c r="J32" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -19428,6 +21177,9 @@
       <c r="I33" t="n">
         <v>93.40000000000001</v>
       </c>
+      <c r="J33" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -19459,6 +21211,9 @@
       <c r="I34" t="n">
         <v>60.2</v>
       </c>
+      <c r="J34" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -19490,6 +21245,9 @@
       <c r="I35" t="n">
         <v>59</v>
       </c>
+      <c r="J35" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -19521,6 +21279,9 @@
       <c r="I36" t="n">
         <v>61.8</v>
       </c>
+      <c r="J36" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -19552,6 +21313,9 @@
       <c r="I37" t="n">
         <v>79.7</v>
       </c>
+      <c r="J37" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -19583,6 +21347,9 @@
       <c r="I38" t="n">
         <v>92.7</v>
       </c>
+      <c r="J38" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -19614,6 +21381,9 @@
       <c r="I39" t="n">
         <v>49.3</v>
       </c>
+      <c r="J39" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -19645,6 +21415,9 @@
       <c r="I40" t="n">
         <v>47.9</v>
       </c>
+      <c r="J40" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -19676,6 +21449,9 @@
       <c r="I41" t="n">
         <v>98.5</v>
       </c>
+      <c r="J41" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -19707,6 +21483,9 @@
       <c r="I42" t="n">
         <v>75.90000000000001</v>
       </c>
+      <c r="J42" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -19738,6 +21517,9 @@
       <c r="I43" t="n">
         <v>60.8</v>
       </c>
+      <c r="J43" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -19769,6 +21551,9 @@
       <c r="I44" t="n">
         <v>40</v>
       </c>
+      <c r="J44" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -19800,6 +21585,9 @@
       <c r="I45" t="n">
         <v>96.8</v>
       </c>
+      <c r="J45" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -19831,6 +21619,9 @@
       <c r="I46" t="n">
         <v>62.4</v>
       </c>
+      <c r="J46" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -19862,6 +21653,9 @@
       <c r="I47" t="n">
         <v>62.7</v>
       </c>
+      <c r="J47" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -19893,6 +21687,9 @@
       <c r="I48" t="n">
         <v>81.09999999999999</v>
       </c>
+      <c r="J48" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -19924,6 +21721,9 @@
       <c r="I49" t="n">
         <v>57.4</v>
       </c>
+      <c r="J49" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -19955,6 +21755,9 @@
       <c r="I50" t="n">
         <v>43</v>
       </c>
+      <c r="J50" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -19986,6 +21789,9 @@
       <c r="I51" t="n">
         <v>54</v>
       </c>
+      <c r="J51" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -20017,6 +21823,9 @@
       <c r="I52" t="n">
         <v>67.8</v>
       </c>
+      <c r="J52" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -20048,6 +21857,9 @@
       <c r="I53" t="n">
         <v>44.3</v>
       </c>
+      <c r="J53" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -20079,6 +21891,9 @@
       <c r="I54" t="n">
         <v>86.09999999999999</v>
       </c>
+      <c r="J54" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -20110,6 +21925,9 @@
       <c r="I55" t="n">
         <v>86.3</v>
       </c>
+      <c r="J55" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -20141,6 +21959,9 @@
       <c r="I56" t="n">
         <v>77.7</v>
       </c>
+      <c r="J56" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -20172,6 +21993,9 @@
       <c r="I57" t="n">
         <v>93.3</v>
       </c>
+      <c r="J57" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -20203,6 +22027,9 @@
       <c r="I58" t="n">
         <v>56.6</v>
       </c>
+      <c r="J58" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -20234,6 +22061,9 @@
       <c r="I59" t="n">
         <v>75.8</v>
       </c>
+      <c r="J59" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -20265,6 +22095,9 @@
       <c r="I60" t="n">
         <v>99.8</v>
       </c>
+      <c r="J60" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -20296,6 +22129,9 @@
       <c r="I61" t="n">
         <v>54</v>
       </c>
+      <c r="J61" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -20327,6 +22163,9 @@
       <c r="I62" t="n">
         <v>81.40000000000001</v>
       </c>
+      <c r="J62" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -20358,6 +22197,9 @@
       <c r="I63" t="n">
         <v>81.8</v>
       </c>
+      <c r="J63" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -20389,6 +22231,9 @@
       <c r="I64" t="n">
         <v>94.90000000000001</v>
       </c>
+      <c r="J64" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -20420,6 +22265,9 @@
       <c r="I65" t="n">
         <v>40</v>
       </c>
+      <c r="J65" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -20451,6 +22299,9 @@
       <c r="I66" t="n">
         <v>54.3</v>
       </c>
+      <c r="J66" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -20482,6 +22333,9 @@
       <c r="I67" t="n">
         <v>73.09999999999999</v>
       </c>
+      <c r="J67" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -20513,6 +22367,9 @@
       <c r="I68" t="n">
         <v>90.09999999999999</v>
       </c>
+      <c r="J68" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -20544,6 +22401,9 @@
       <c r="I69" t="n">
         <v>90.2</v>
       </c>
+      <c r="J69" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -20575,6 +22435,9 @@
       <c r="I70" t="n">
         <v>44.3</v>
       </c>
+      <c r="J70" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -20606,6 +22469,9 @@
       <c r="I71" t="n">
         <v>43.6</v>
       </c>
+      <c r="J71" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -20637,6 +22503,9 @@
       <c r="I72" t="n">
         <v>55.9</v>
       </c>
+      <c r="J72" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -20668,6 +22537,9 @@
       <c r="I73" t="n">
         <v>83.5</v>
       </c>
+      <c r="J73" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -20699,6 +22571,9 @@
       <c r="I74" t="n">
         <v>85</v>
       </c>
+      <c r="J74" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -20730,6 +22605,9 @@
       <c r="I75" t="n">
         <v>93</v>
       </c>
+      <c r="J75" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -20761,6 +22639,9 @@
       <c r="I76" t="n">
         <v>66.59999999999999</v>
       </c>
+      <c r="J76" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -20792,6 +22673,9 @@
       <c r="I77" t="n">
         <v>65.8</v>
       </c>
+      <c r="J77" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -20823,6 +22707,9 @@
       <c r="I78" t="n">
         <v>55.2</v>
       </c>
+      <c r="J78" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -20854,6 +22741,9 @@
       <c r="I79" t="n">
         <v>71.09999999999999</v>
       </c>
+      <c r="J79" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -20885,6 +22775,9 @@
       <c r="I80" t="n">
         <v>89.3</v>
       </c>
+      <c r="J80" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -20916,6 +22809,9 @@
       <c r="I81" t="n">
         <v>42.3</v>
       </c>
+      <c r="J81" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -20947,6 +22843,9 @@
       <c r="I82" t="n">
         <v>45.5</v>
       </c>
+      <c r="J82" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -20978,6 +22877,9 @@
       <c r="I83" t="n">
         <v>89.5</v>
       </c>
+      <c r="J83" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -21009,6 +22911,9 @@
       <c r="I84" t="n">
         <v>74.59999999999999</v>
       </c>
+      <c r="J84" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -21040,6 +22945,9 @@
       <c r="I85" t="n">
         <v>92.09999999999999</v>
       </c>
+      <c r="J85" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -21071,6 +22979,9 @@
       <c r="I86" t="n">
         <v>62.9</v>
       </c>
+      <c r="J86" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -21102,6 +23013,9 @@
       <c r="I87" t="n">
         <v>43</v>
       </c>
+      <c r="J87" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -21133,6 +23047,9 @@
       <c r="I88" t="n">
         <v>57.4</v>
       </c>
+      <c r="J88" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -21164,6 +23081,9 @@
       <c r="I89" t="n">
         <v>45.1</v>
       </c>
+      <c r="J89" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -21195,6 +23115,9 @@
       <c r="I90" t="n">
         <v>79.09999999999999</v>
       </c>
+      <c r="J90" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -21225,6 +23148,9 @@
       </c>
       <c r="I91" t="n">
         <v>59.4</v>
+      </c>
+      <c r="J91" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -21238,7 +23164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21292,6 +23218,11 @@
           <t>Final Exam</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Assessments Completed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -21326,6 +23257,9 @@
       <c r="J2" t="n">
         <v>41.5</v>
       </c>
+      <c r="K2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -21360,6 +23294,9 @@
       <c r="J3" t="n">
         <v>89.09999999999999</v>
       </c>
+      <c r="K3" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21394,6 +23331,9 @@
       <c r="J4" t="n">
         <v>95.59999999999999</v>
       </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -21428,6 +23368,9 @@
       <c r="J5" t="n">
         <v>52.5</v>
       </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -21462,6 +23405,9 @@
       <c r="J6" t="n">
         <v>81.90000000000001</v>
       </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -21496,6 +23442,9 @@
       <c r="J7" t="n">
         <v>77.09999999999999</v>
       </c>
+      <c r="K7" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -21530,6 +23479,9 @@
       <c r="J8" t="n">
         <v>91.90000000000001</v>
       </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -21564,6 +23516,9 @@
       <c r="J9" t="n">
         <v>58.9</v>
       </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -21598,6 +23553,9 @@
       <c r="J10" t="n">
         <v>54.8</v>
       </c>
+      <c r="K10" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -21632,6 +23590,9 @@
       <c r="J11" t="n">
         <v>54.2</v>
       </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21666,6 +23627,9 @@
       <c r="J12" t="n">
         <v>41.8</v>
       </c>
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -21700,6 +23664,9 @@
       <c r="J13" t="n">
         <v>97.59999999999999</v>
       </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -21734,6 +23701,9 @@
       <c r="J14" t="n">
         <v>59.8</v>
       </c>
+      <c r="K14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -21768,6 +23738,9 @@
       <c r="J15" t="n">
         <v>82.3</v>
       </c>
+      <c r="K15" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -21802,6 +23775,9 @@
       <c r="J16" t="n">
         <v>59</v>
       </c>
+      <c r="K16" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -21836,6 +23812,9 @@
       <c r="J17" t="n">
         <v>92.8</v>
       </c>
+      <c r="K17" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -21870,6 +23849,9 @@
       <c r="J18" t="n">
         <v>86.7</v>
       </c>
+      <c r="K18" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -21904,6 +23886,9 @@
       <c r="J19" t="n">
         <v>53.9</v>
       </c>
+      <c r="K19" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -21938,6 +23923,9 @@
       <c r="J20" t="n">
         <v>62.4</v>
       </c>
+      <c r="K20" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -21972,6 +23960,9 @@
       <c r="J21" t="n">
         <v>56.2</v>
       </c>
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -22006,6 +23997,9 @@
       <c r="J22" t="n">
         <v>92</v>
       </c>
+      <c r="K22" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -22040,6 +24034,9 @@
       <c r="J23" t="n">
         <v>62.8</v>
       </c>
+      <c r="K23" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -22074,6 +24071,9 @@
       <c r="J24" t="n">
         <v>71.2</v>
       </c>
+      <c r="K24" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -22108,6 +24108,9 @@
       <c r="J25" t="n">
         <v>73.5</v>
       </c>
+      <c r="K25" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -22142,6 +24145,9 @@
       <c r="J26" t="n">
         <v>67.7</v>
       </c>
+      <c r="K26" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -22176,6 +24182,9 @@
       <c r="J27" t="n">
         <v>83.40000000000001</v>
       </c>
+      <c r="K27" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -22210,6 +24219,9 @@
       <c r="J28" t="n">
         <v>50.7</v>
       </c>
+      <c r="K28" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -22244,6 +24256,9 @@
       <c r="J29" t="n">
         <v>87.8</v>
       </c>
+      <c r="K29" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -22278,6 +24293,9 @@
       <c r="J30" t="n">
         <v>87.5</v>
       </c>
+      <c r="K30" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -22312,6 +24330,9 @@
       <c r="J31" t="n">
         <v>79.59999999999999</v>
       </c>
+      <c r="K31" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -22346,6 +24367,9 @@
       <c r="J32" t="n">
         <v>66.8</v>
       </c>
+      <c r="K32" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -22380,6 +24404,9 @@
       <c r="J33" t="n">
         <v>91.3</v>
       </c>
+      <c r="K33" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -22414,6 +24441,9 @@
       <c r="J34" t="n">
         <v>44.8</v>
       </c>
+      <c r="K34" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -22448,6 +24478,9 @@
       <c r="J35" t="n">
         <v>48.9</v>
       </c>
+      <c r="K35" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -22482,6 +24515,9 @@
       <c r="J36" t="n">
         <v>42.9</v>
       </c>
+      <c r="K36" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -22516,6 +24552,9 @@
       <c r="J37" t="n">
         <v>50.6</v>
       </c>
+      <c r="K37" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -22550,6 +24589,9 @@
       <c r="J38" t="n">
         <v>44.1</v>
       </c>
+      <c r="K38" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -22584,6 +24626,9 @@
       <c r="J39" t="n">
         <v>71.5</v>
       </c>
+      <c r="K39" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -22618,6 +24663,9 @@
       <c r="J40" t="n">
         <v>81.3</v>
       </c>
+      <c r="K40" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -22652,6 +24700,9 @@
       <c r="J41" t="n">
         <v>61.2</v>
       </c>
+      <c r="K41" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -22686,6 +24737,9 @@
       <c r="J42" t="n">
         <v>82.5</v>
       </c>
+      <c r="K42" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -22720,6 +24774,9 @@
       <c r="J43" t="n">
         <v>99.90000000000001</v>
       </c>
+      <c r="K43" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -22754,6 +24811,9 @@
       <c r="J44" t="n">
         <v>87.40000000000001</v>
       </c>
+      <c r="K44" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -22788,6 +24848,9 @@
       <c r="J45" t="n">
         <v>77</v>
       </c>
+      <c r="K45" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -22822,6 +24885,9 @@
       <c r="J46" t="n">
         <v>78.7</v>
       </c>
+      <c r="K46" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -22856,6 +24922,9 @@
       <c r="J47" t="n">
         <v>84.59999999999999</v>
       </c>
+      <c r="K47" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -22890,6 +24959,9 @@
       <c r="J48" t="n">
         <v>88</v>
       </c>
+      <c r="K48" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -22924,6 +24996,9 @@
       <c r="J49" t="n">
         <v>90.5</v>
       </c>
+      <c r="K49" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -22958,6 +25033,9 @@
       <c r="J50" t="n">
         <v>41.9</v>
       </c>
+      <c r="K50" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -22992,6 +25070,9 @@
       <c r="J51" t="n">
         <v>46.7</v>
       </c>
+      <c r="K51" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -23026,6 +25107,9 @@
       <c r="J52" t="n">
         <v>51.4</v>
       </c>
+      <c r="K52" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -23060,6 +25144,9 @@
       <c r="J53" t="n">
         <v>96.3</v>
       </c>
+      <c r="K53" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -23094,6 +25181,9 @@
       <c r="J54" t="n">
         <v>95.90000000000001</v>
       </c>
+      <c r="K54" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -23128,6 +25218,9 @@
       <c r="J55" t="n">
         <v>58.7</v>
       </c>
+      <c r="K55" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -23162,6 +25255,9 @@
       <c r="J56" t="n">
         <v>66.5</v>
       </c>
+      <c r="K56" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -23196,6 +25292,9 @@
       <c r="J57" t="n">
         <v>61</v>
       </c>
+      <c r="K57" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -23230,6 +25329,9 @@
       <c r="J58" t="n">
         <v>60.3</v>
       </c>
+      <c r="K58" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -23264,6 +25366,9 @@
       <c r="J59" t="n">
         <v>50.7</v>
       </c>
+      <c r="K59" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -23298,6 +25403,9 @@
       <c r="J60" t="n">
         <v>82.8</v>
       </c>
+      <c r="K60" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -23332,6 +25440,9 @@
       <c r="J61" t="n">
         <v>95.2</v>
       </c>
+      <c r="K61" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -23366,6 +25477,9 @@
       <c r="J62" t="n">
         <v>91.7</v>
       </c>
+      <c r="K62" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -23400,6 +25514,9 @@
       <c r="J63" t="n">
         <v>67.2</v>
       </c>
+      <c r="K63" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -23434,6 +25551,9 @@
       <c r="J64" t="n">
         <v>47.6</v>
       </c>
+      <c r="K64" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -23468,6 +25588,9 @@
       <c r="J65" t="n">
         <v>64</v>
       </c>
+      <c r="K65" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -23502,6 +25625,9 @@
       <c r="J66" t="n">
         <v>75.5</v>
       </c>
+      <c r="K66" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -23536,6 +25662,9 @@
       <c r="J67" t="n">
         <v>95.90000000000001</v>
       </c>
+      <c r="K67" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -23570,6 +25699,9 @@
       <c r="J68" t="n">
         <v>97.40000000000001</v>
       </c>
+      <c r="K68" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -23604,6 +25736,9 @@
       <c r="J69" t="n">
         <v>45.4</v>
       </c>
+      <c r="K69" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -23638,6 +25773,9 @@
       <c r="J70" t="n">
         <v>71.90000000000001</v>
       </c>
+      <c r="K70" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -23672,6 +25810,9 @@
       <c r="J71" t="n">
         <v>58.3</v>
       </c>
+      <c r="K71" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -23706,6 +25847,9 @@
       <c r="J72" t="n">
         <v>64.3</v>
       </c>
+      <c r="K72" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -23740,6 +25884,9 @@
       <c r="J73" t="n">
         <v>61.6</v>
       </c>
+      <c r="K73" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -23774,6 +25921,9 @@
       <c r="J74" t="n">
         <v>62.9</v>
       </c>
+      <c r="K74" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -23808,6 +25958,9 @@
       <c r="J75" t="n">
         <v>49.3</v>
       </c>
+      <c r="K75" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -23842,6 +25995,9 @@
       <c r="J76" t="n">
         <v>66.2</v>
       </c>
+      <c r="K76" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -23876,6 +26032,9 @@
       <c r="J77" t="n">
         <v>65.5</v>
       </c>
+      <c r="K77" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -23910,6 +26069,9 @@
       <c r="J78" t="n">
         <v>74.7</v>
       </c>
+      <c r="K78" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -23944,6 +26106,9 @@
       <c r="J79" t="n">
         <v>74.09999999999999</v>
       </c>
+      <c r="K79" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -23978,6 +26143,9 @@
       <c r="J80" t="n">
         <v>99</v>
       </c>
+      <c r="K80" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -24012,6 +26180,9 @@
       <c r="J81" t="n">
         <v>97.59999999999999</v>
       </c>
+      <c r="K81" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -24046,6 +26217,9 @@
       <c r="J82" t="n">
         <v>68.09999999999999</v>
       </c>
+      <c r="K82" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -24080,6 +26254,9 @@
       <c r="J83" t="n">
         <v>42.1</v>
       </c>
+      <c r="K83" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -24114,6 +26291,9 @@
       <c r="J84" t="n">
         <v>43.1</v>
       </c>
+      <c r="K84" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -24148,6 +26328,9 @@
       <c r="J85" t="n">
         <v>56.7</v>
       </c>
+      <c r="K85" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -24182,6 +26365,9 @@
       <c r="J86" t="n">
         <v>49.1</v>
       </c>
+      <c r="K86" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -24216,6 +26402,9 @@
       <c r="J87" t="n">
         <v>60.6</v>
       </c>
+      <c r="K87" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -24250,6 +26439,9 @@
       <c r="J88" t="n">
         <v>54.3</v>
       </c>
+      <c r="K88" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -24284,6 +26476,9 @@
       <c r="J89" t="n">
         <v>47</v>
       </c>
+      <c r="K89" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -24318,6 +26513,9 @@
       <c r="J90" t="n">
         <v>82.3</v>
       </c>
+      <c r="K90" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -24352,6 +26550,9 @@
       <c r="J91" t="n">
         <v>97.7</v>
       </c>
+      <c r="K91" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -24385,6 +26586,9 @@
       </c>
       <c r="J92" t="n">
         <v>94</v>
+      </c>
+      <c r="K92" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
